--- a/Data/ModelResponse/4/evaluation/4_evaluation_summary.xlsx
+++ b/Data/ModelResponse/4/evaluation/4_evaluation_summary.xlsx
@@ -536,46 +536,46 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7955208333333333</v>
+        <v>0.7877604166666666</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7955208333333333</v>
+        <v>0.7877604166666666</v>
       </c>
       <c r="H2" t="n">
         <v>9554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7780082987551867</v>
+        <v>0.785572813509851</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8242620891773079</v>
+        <v>0.7887795687670086</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8004675747103071</v>
+        <v>0.7871729252624432</v>
       </c>
       <c r="L2" t="n">
         <v>9646</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8150473672615114</v>
+        <v>0.789944831893411</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7670537010159652</v>
+        <v>0.7867509848641924</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.7883446735573676</v>
       </c>
       <c r="P2" t="n">
-        <v>7875</v>
+        <v>7536</v>
       </c>
       <c r="Q2" t="n">
-        <v>1679</v>
+        <v>2018</v>
       </c>
       <c r="R2" t="n">
-        <v>2247</v>
+        <v>2057</v>
       </c>
       <c r="S2" t="n">
-        <v>7399</v>
+        <v>7589</v>
       </c>
     </row>
   </sheetData>
@@ -708,46 +708,46 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.84</v>
+        <v>0.8412500000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.84</v>
+        <v>0.8412500000000001</v>
       </c>
       <c r="H2" t="n">
         <v>387</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8018648018648019</v>
+        <v>0.8125</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8733850129198967</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8431372549019609</v>
+        <v>0.841843088418431</v>
       </c>
       <c r="L2" t="n">
         <v>413</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8840970350404312</v>
+        <v>0.8723958333333334</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7941888619854721</v>
+        <v>0.8111380145278451</v>
       </c>
       <c r="O2" t="n">
-        <v>0.836734693877551</v>
+        <v>0.8406524466750315</v>
       </c>
       <c r="P2" t="n">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R2" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="S2" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
@@ -769,46 +769,46 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8625</v>
+        <v>0.86875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8625</v>
+        <v>0.86875</v>
       </c>
       <c r="H3" t="n">
         <v>404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.831081081081081</v>
+        <v>0.8585131894484412</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9133663366336634</v>
+        <v>0.8861386138613861</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8702830188679245</v>
+        <v>0.8721071863580999</v>
       </c>
       <c r="L3" t="n">
         <v>396</v>
       </c>
       <c r="M3" t="n">
-        <v>0.901685393258427</v>
+        <v>0.8798955613577023</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8106060606060606</v>
+        <v>0.851010101010101</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8537234042553191</v>
+        <v>0.865211810012837</v>
       </c>
       <c r="P3" t="n">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R3" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="S3" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">
@@ -830,46 +830,46 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.64375</v>
+        <v>0.650625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.64375</v>
+        <v>0.650625</v>
       </c>
       <c r="H4" t="n">
         <v>821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6881559220389805</v>
+        <v>0.7003058103975535</v>
       </c>
       <c r="J4" t="n">
-        <v>0.559074299634592</v>
+        <v>0.5578562728380024</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6169354838709677</v>
+        <v>0.6210169491525424</v>
       </c>
       <c r="L4" t="n">
         <v>779</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6120042872454448</v>
+        <v>0.6162790697674418</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7329910141206675</v>
+        <v>0.748395378690629</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6670560747663551</v>
+        <v>0.6759420289855073</v>
       </c>
       <c r="P4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q4" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="R4" t="n">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="S4" t="n">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5">
@@ -891,46 +891,46 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.729375</v>
+        <v>0.7225</v>
       </c>
       <c r="G5" t="n">
-        <v>0.729375</v>
+        <v>0.7225</v>
       </c>
       <c r="H5" t="n">
         <v>805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6905737704918032</v>
+        <v>0.6964091403699674</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8372670807453416</v>
+        <v>0.7950310559006211</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7568781583380123</v>
+        <v>0.74245939675174</v>
       </c>
       <c r="L5" t="n">
         <v>795</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7900641025641025</v>
+        <v>0.7577092511013216</v>
       </c>
       <c r="N5" t="n">
-        <v>0.620125786163522</v>
+        <v>0.6490566037735849</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6948555320648344</v>
+        <v>0.6991869918699187</v>
       </c>
       <c r="P5" t="n">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="Q5" t="n">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="R5" t="n">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="S5" t="n">
-        <v>493</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6">
@@ -952,46 +952,46 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.803125</v>
+        <v>0.808125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.803125</v>
+        <v>0.808125</v>
       </c>
       <c r="H6" t="n">
         <v>821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7640918580375783</v>
+        <v>0.7799564270152506</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8915956151035322</v>
+        <v>0.8721071863580999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8229342327150083</v>
+        <v>0.8234617596319724</v>
       </c>
       <c r="L6" t="n">
         <v>779</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8613707165109035</v>
+        <v>0.8460410557184751</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7098844672657253</v>
+        <v>0.7406931964056482</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7783251231527093</v>
+        <v>0.7898699520876113</v>
       </c>
       <c r="P6" t="n">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="Q6" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="R6" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="S6" t="n">
-        <v>553</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7">
@@ -1013,46 +1013,46 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.94625</v>
+        <v>0.904375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.94625</v>
+        <v>0.904375</v>
       </c>
       <c r="H7" t="n">
         <v>740</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9192307692307692</v>
+        <v>0.880674448767834</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9689189189189189</v>
+        <v>0.9175675675675675</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9434210526315788</v>
+        <v>0.8987425545996028</v>
       </c>
       <c r="L7" t="n">
         <v>860</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9719512195121951</v>
+        <v>0.9264173703256936</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9267441860465117</v>
+        <v>0.8930232558139535</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9488095238095238</v>
+        <v>0.9094138543516874</v>
       </c>
       <c r="P7" t="n">
-        <v>717</v>
+        <v>679</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S7" t="n">
-        <v>797</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -1074,46 +1074,46 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.939375</v>
+        <v>0.92375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.939375</v>
+        <v>0.92375</v>
       </c>
       <c r="H8" t="n">
         <v>769</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9231738035264484</v>
+        <v>0.9089759797724399</v>
       </c>
       <c r="J8" t="n">
-        <v>0.953185955786736</v>
+        <v>0.9349804941482445</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9379398592450416</v>
+        <v>0.9217948717948719</v>
       </c>
       <c r="L8" t="n">
         <v>831</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9553349875930521</v>
+        <v>0.9381953028430161</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9265944645006017</v>
+        <v>0.9133574007220217</v>
       </c>
       <c r="O8" t="n">
-        <v>0.940745265729994</v>
+        <v>0.925609756097561</v>
       </c>
       <c r="P8" t="n">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="Q8" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="S8" t="n">
-        <v>770</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9">
@@ -1135,46 +1135,46 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.738125</v>
+        <v>0.724375</v>
       </c>
       <c r="G9" t="n">
-        <v>0.738125</v>
+        <v>0.724375</v>
       </c>
       <c r="H9" t="n">
         <v>822</v>
       </c>
       <c r="I9" t="n">
-        <v>0.71413390010627</v>
+        <v>0.7063921993499458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8175182481751825</v>
+        <v>0.7931873479318735</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7623369256948384</v>
+        <v>0.7472779369627508</v>
       </c>
       <c r="L9" t="n">
         <v>778</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7723823975720789</v>
+        <v>0.7488921713441654</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6542416452442159</v>
+        <v>0.6516709511568124</v>
       </c>
       <c r="O9" t="n">
-        <v>0.708420320111343</v>
+        <v>0.6969072164948454</v>
       </c>
       <c r="P9" t="n">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="Q9" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="R9" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S9" t="n">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10">
@@ -1196,46 +1196,46 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.850625</v>
+        <v>0.844375</v>
       </c>
       <c r="G10" t="n">
-        <v>0.850625</v>
+        <v>0.844375</v>
       </c>
       <c r="H10" t="n">
         <v>804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.798941798941799</v>
+        <v>0.8073089700996677</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9390547263681592</v>
+        <v>0.9067164179104478</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8633504859919955</v>
+        <v>0.8541300527240773</v>
       </c>
       <c r="L10" t="n">
         <v>796</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9251908396946565</v>
+        <v>0.8923959827833573</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7613065326633166</v>
+        <v>0.7814070351758794</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8352860096485184</v>
+        <v>0.8332217012726055</v>
       </c>
       <c r="P10" t="n">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="R10" t="n">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="S10" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11">
@@ -1257,46 +1257,46 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7</v>
+        <v>0.7006250000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.7006250000000001</v>
       </c>
       <c r="H11" t="n">
         <v>812</v>
       </c>
       <c r="I11" t="n">
-        <v>0.716710182767624</v>
+        <v>0.7335203366058906</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6761083743842364</v>
+        <v>0.6440886699507389</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6958174904942965</v>
+        <v>0.6859016393442622</v>
       </c>
       <c r="L11" t="n">
         <v>788</v>
       </c>
       <c r="M11" t="n">
-        <v>0.684652278177458</v>
+        <v>0.6741826381059752</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7246192893401016</v>
+        <v>0.7588832487309645</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7040690505548706</v>
+        <v>0.7140298507462687</v>
       </c>
       <c r="P11" t="n">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="Q11" t="n">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="R11" t="n">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="S11" t="n">
-        <v>571</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12">
@@ -1318,46 +1318,46 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.86875</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.86875</v>
       </c>
       <c r="H12" t="n">
         <v>788</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9066852367688022</v>
+        <v>0.9176300578034682</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8261421319796954</v>
+        <v>0.8058375634517766</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8645418326693227</v>
+        <v>0.858108108108108</v>
       </c>
       <c r="L12" t="n">
         <v>812</v>
       </c>
       <c r="M12" t="n">
-        <v>0.844671201814059</v>
+        <v>0.8314977973568282</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9174876847290641</v>
+        <v>0.9298029556650246</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8795749704840614</v>
+        <v>0.8779069767441861</v>
       </c>
       <c r="P12" t="n">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="Q12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="S12" t="n">
-        <v>745</v>
+        <v>755</v>
       </c>
     </row>
     <row r="13">
@@ -1379,46 +1379,46 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.716875</v>
+        <v>0.7175</v>
       </c>
       <c r="G13" t="n">
-        <v>0.716875</v>
+        <v>0.7175</v>
       </c>
       <c r="H13" t="n">
         <v>813</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>0.7187878787878788</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7749077490774908</v>
+        <v>0.7293972939729397</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7355516637478109</v>
+        <v>0.7240537240537239</v>
       </c>
       <c r="L13" t="n">
         <v>787</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7385714285714285</v>
+        <v>0.7161290322580646</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6569250317662008</v>
+        <v>0.7052096569250318</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6953597848016139</v>
+        <v>0.7106274007682459</v>
       </c>
       <c r="P13" t="n">
-        <v>630</v>
+        <v>593</v>
       </c>
       <c r="Q13" t="n">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="R13" t="n">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="S13" t="n">
-        <v>517</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14">
@@ -1440,46 +1440,46 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755</v>
+        <v>0.733125</v>
       </c>
       <c r="G14" t="n">
-        <v>0.755</v>
+        <v>0.733125</v>
       </c>
       <c r="H14" t="n">
         <v>768</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7338308457711443</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7682291666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7506361323155216</v>
+        <v>0.6990838618745595</v>
       </c>
       <c r="L14" t="n">
         <v>832</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7763819095477387</v>
+        <v>0.7133825079030558</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7427884615384616</v>
+        <v>0.8137019230769231</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7592137592137592</v>
+        <v>0.7602470522178552</v>
       </c>
       <c r="P14" t="n">
-        <v>590</v>
+        <v>496</v>
       </c>
       <c r="Q14" t="n">
-        <v>178</v>
+        <v>272</v>
       </c>
       <c r="R14" t="n">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="S14" t="n">
-        <v>618</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -1612,46 +1612,46 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.75</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>0.75</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="H2" t="n">
         <v>89</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7070707070707071</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7865168539325843</v>
+        <v>0.7303370786516854</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7446808510638298</v>
+        <v>0.7471264367816092</v>
       </c>
       <c r="L2" t="n">
         <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7956989247311828</v>
+        <v>0.7757009345794392</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7184466019417476</v>
+        <v>0.8058252427184466</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7551020408163266</v>
+        <v>0.7904761904761904</v>
       </c>
       <c r="P2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="S2" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -1673,46 +1673,46 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8279569892473119</v>
+        <v>0.6989247311827957</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7344632768361582</v>
       </c>
       <c r="L3" t="n">
         <v>99</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8279569892473119</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8080808080808081</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7729468599033815</v>
       </c>
       <c r="P3" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="R3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="S3" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -1734,46 +1734,46 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
         <v>110</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8363636363636363</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8558139534883721</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="L4" t="n">
         <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8414634146341463</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8165680473372782</v>
+        <v>0.8048780487804877</v>
       </c>
       <c r="P4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S4" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -1795,46 +1795,46 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.765625</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765625</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="H5" t="n">
         <v>97</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7452830188679245</v>
+        <v>0.7155963302752294</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8144329896907216</v>
+        <v>0.8041237113402062</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7783251231527093</v>
+        <v>0.7572815533980584</v>
       </c>
       <c r="L5" t="n">
         <v>95</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.7710843373493976</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7157894736842105</v>
+        <v>0.6736842105263158</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7513812154696132</v>
+        <v>0.7191011235955056</v>
       </c>
       <c r="P5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -1856,46 +1856,46 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="H6" t="n">
         <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.8602150537634409</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8252427184466019</v>
+        <v>0.7766990291262136</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.8163265306122449</v>
       </c>
       <c r="L6" t="n">
         <v>89</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.7676767676767676</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8426966292134831</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8241758241758241</v>
+        <v>0.8085106382978724</v>
       </c>
       <c r="P6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1917,34 +1917,34 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H7" t="n">
         <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7596153846153846</v>
       </c>
       <c r="J7" t="n">
         <v>0.8404255319148937</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8102564102564104</v>
+        <v>0.7979797979797979</v>
       </c>
       <c r="L7" t="n">
         <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.8295454545454546</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7755102040816326</v>
+        <v>0.7448979591836735</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8042328042328042</v>
+        <v>0.7849462365591399</v>
       </c>
       <c r="P7" t="n">
         <v>79</v>
@@ -1953,10 +1953,10 @@
         <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S7" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -1978,46 +1978,46 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="H8" t="n">
         <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.8478260869565217</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8618784530386741</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8640776699029126</v>
       </c>
       <c r="N8" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8679245283018867</v>
+        <v>0.8768472906403941</v>
       </c>
       <c r="P8" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -2039,46 +2039,46 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.828125</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.828125</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H9" t="n">
         <v>104</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8736842105263158</v>
+        <v>0.8484848484848485</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7980769230769231</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8341708542713568</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L9" t="n">
         <v>88</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7835051546391752</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8295454545454546</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8216216216216216</v>
+        <v>0.8066298342541436</v>
       </c>
       <c r="P9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S9" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -2100,46 +2100,46 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7552083333333334</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7552083333333334</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H10" t="n">
         <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>0.780952380952381</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7641509433962265</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7772511848341234</v>
+        <v>0.7363636363636363</v>
       </c>
       <c r="L10" t="n">
         <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6794871794871795</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7325581395348837</v>
+        <v>0.6162790697674418</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7283236994219654</v>
+        <v>0.6463414634146342</v>
       </c>
       <c r="P10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="S10" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -2161,46 +2161,46 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="H11" t="n">
         <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7433628318584071</v>
+        <v>0.7653061224489796</v>
       </c>
       <c r="J11" t="n">
-        <v>0.875</v>
+        <v>0.78125</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8038277511961722</v>
+        <v>0.7731958762886597</v>
       </c>
       <c r="L11" t="n">
         <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8481012658227848</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7684210526315789</v>
       </c>
       <c r="P11" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S11" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -2222,46 +2222,46 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="H12" t="n">
         <v>96</v>
       </c>
       <c r="I12" t="n">
-        <v>0.75</v>
+        <v>0.8375</v>
       </c>
       <c r="J12" t="n">
-        <v>0.78125</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7613636363636364</v>
       </c>
       <c r="L12" t="n">
         <v>96</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7717391304347826</v>
+        <v>0.7410714285714286</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7553191489361701</v>
+        <v>0.7980769230769232</v>
       </c>
       <c r="P12" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R12" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="S12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -2283,46 +2283,46 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.75</v>
       </c>
       <c r="H13" t="n">
         <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7789473684210526</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>0.774869109947644</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="L13" t="n">
         <v>96</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N13" t="n">
-        <v>0.78125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7772020725388602</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="P13" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -2344,46 +2344,46 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.75</v>
       </c>
       <c r="H14" t="n">
         <v>109</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7830188679245284</v>
+        <v>0.8279569892473119</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7614678899082569</v>
+        <v>0.7064220183486238</v>
       </c>
       <c r="K14" t="n">
-        <v>0.772093023255814</v>
+        <v>0.7623762376237624</v>
       </c>
       <c r="L14" t="n">
         <v>83</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.6767676767676768</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7228915662650602</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7100591715976331</v>
+        <v>0.7362637362637363</v>
       </c>
       <c r="P14" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="S14" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -2405,46 +2405,46 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.671875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G15" t="n">
-        <v>0.671875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H15" t="n">
         <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6165413533834586</v>
+        <v>0.6403508771929824</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8723404255319149</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7224669603524227</v>
+        <v>0.7019230769230769</v>
       </c>
       <c r="L15" t="n">
         <v>98</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4795918367346939</v>
+        <v>0.5816326530612245</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5987261146496815</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="P15" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="R15" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="S15" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -2466,46 +2466,46 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="H16" t="n">
         <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7289719626168224</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7918781725888325</v>
+        <v>0.7524752475247526</v>
       </c>
       <c r="L16" t="n">
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8588235294117647</v>
+        <v>0.825</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7156862745098039</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7807486631016043</v>
+        <v>0.7252747252747253</v>
       </c>
       <c r="P16" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S16" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -2527,46 +2527,46 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="H17" t="n">
         <v>81</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7415730337078652</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="L17" t="n">
         <v>111</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8543689320388349</v>
+        <v>0.825</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7927927927927928</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8224299065420561</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="P17" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
@@ -2588,46 +2588,46 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6927083333333334</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6927083333333334</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="H18" t="n">
         <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6949152542372882</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="J18" t="n">
-        <v>0.780952380952381</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7354260089686099</v>
+        <v>0.6965174129353233</v>
       </c>
       <c r="L18" t="n">
         <v>87</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6891891891891891</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.7011494252873564</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6335403726708073</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P18" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R18" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="S18" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -2649,46 +2649,46 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.796875</v>
+        <v>0.765625</v>
       </c>
       <c r="G19" t="n">
-        <v>0.796875</v>
+        <v>0.765625</v>
       </c>
       <c r="H19" t="n">
         <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8625</v>
+        <v>0.8170731707317073</v>
       </c>
       <c r="J19" t="n">
-        <v>0.711340206185567</v>
+        <v>0.6907216494845361</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.7486033519553071</v>
       </c>
       <c r="L19" t="n">
         <v>95</v>
       </c>
       <c r="M19" t="n">
-        <v>0.75</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8842105263157894</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8115942028985507</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P19" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S19" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -2710,46 +2710,46 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H20" t="n">
         <v>83</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J20" t="n">
-        <v>0.927710843373494</v>
+        <v>0.963855421686747</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8603351955307261</v>
+        <v>0.8510638297872339</v>
       </c>
       <c r="L20" t="n">
         <v>109</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9375</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8256880733944955</v>
+        <v>0.7706422018348624</v>
       </c>
       <c r="O20" t="n">
-        <v>0.878048780487805</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="P20" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="S20" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
@@ -2771,34 +2771,34 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="H21" t="n">
         <v>99</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.7980769230769231</v>
       </c>
       <c r="J21" t="n">
         <v>0.8383838383838383</v>
       </c>
       <c r="K21" t="n">
-        <v>0.83</v>
+        <v>0.8177339901477833</v>
       </c>
       <c r="L21" t="n">
         <v>93</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8241758241758241</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8152173913043477</v>
+        <v>0.7955801104972376</v>
       </c>
       <c r="P21" t="n">
         <v>83</v>
@@ -2807,10 +2807,10 @@
         <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -2832,46 +2832,46 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="H22" t="n">
         <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8117647058823529</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8313253012048193</v>
+        <v>0.7973856209150327</v>
       </c>
       <c r="L22" t="n">
         <v>111</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8878504672897196</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8558558558558559</v>
+        <v>0.9009009009009009</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8715596330275229</v>
+        <v>0.8658008658008659</v>
       </c>
       <c r="P22" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -2893,46 +2893,46 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="H23" t="n">
         <v>84</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7040816326530612</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7582417582417582</v>
+        <v>0.7640449438202246</v>
       </c>
       <c r="L23" t="n">
         <v>108</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8404255319148937</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7314814814814815</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7821782178217823</v>
+        <v>0.796116504854369</v>
       </c>
       <c r="P23" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S23" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
@@ -2954,46 +2954,46 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8125</v>
+        <v>0.828125</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8125</v>
+        <v>0.828125</v>
       </c>
       <c r="H24" t="n">
         <v>88</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7956989247311828</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8522727272727273</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8176795580110496</v>
       </c>
       <c r="L24" t="n">
         <v>104</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.8585858585858586</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7788461538461539</v>
+        <v>0.8173076923076923</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8181818181818181</v>
+        <v>0.8374384236453203</v>
       </c>
       <c r="P24" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="S24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -3024,37 +3024,37 @@
         <v>99</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7410714285714286</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8383838383838383</v>
+        <v>0.7171717171717171</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7867298578199051</v>
+        <v>0.7593582887700534</v>
       </c>
       <c r="L25" t="n">
         <v>93</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6881720430107527</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7398843930635839</v>
+        <v>0.7715736040609137</v>
       </c>
       <c r="P25" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="S25" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
@@ -3076,46 +3076,46 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.796875</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="G26" t="n">
-        <v>0.796875</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="H26" t="n">
         <v>87</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8735632183908046</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7958115183246074</v>
+        <v>0.7653061224489797</v>
       </c>
       <c r="L26" t="n">
         <v>105</v>
       </c>
       <c r="M26" t="n">
-        <v>0.875</v>
+        <v>0.8554216867469879</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7979274611398963</v>
+        <v>0.7553191489361701</v>
       </c>
       <c r="P26" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R26" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S26" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
@@ -3137,46 +3137,46 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="H27" t="n">
         <v>101</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8173076923076923</v>
+        <v>0.8617021276595744</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.8307692307692307</v>
       </c>
       <c r="L27" t="n">
         <v>91</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="N27" t="n">
-        <v>0.7912087912087912</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8044692737430168</v>
+        <v>0.8253968253968254</v>
       </c>
       <c r="P27" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="S27" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28">
@@ -3207,37 +3207,37 @@
         <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8404255319148937</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8315789473684211</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.835978835978836</v>
+        <v>0.8306010928961749</v>
       </c>
       <c r="L28" t="n">
         <v>97</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8173076923076923</v>
       </c>
       <c r="N28" t="n">
-        <v>0.845360824742268</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8410256410256411</v>
+        <v>0.845771144278607</v>
       </c>
       <c r="P28" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S28" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
@@ -3259,40 +3259,40 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.765625</v>
+        <v>0.75</v>
       </c>
       <c r="G29" t="n">
-        <v>0.765625</v>
+        <v>0.75</v>
       </c>
       <c r="H29" t="n">
         <v>90</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7064220183486238</v>
+        <v>0.6981132075471698</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8555555555555555</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7738693467336683</v>
+        <v>0.7551020408163266</v>
       </c>
       <c r="L29" t="n">
         <v>102</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="N29" t="n">
         <v>0.6862745098039216</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.7446808510638299</v>
       </c>
       <c r="P29" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R29" t="n">
         <v>32</v>
@@ -3320,46 +3320,46 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.734375</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>0.734375</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="H30" t="n">
         <v>99</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7605633802816901</v>
+        <v>0.75</v>
       </c>
       <c r="L30" t="n">
         <v>93</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7362637362637363</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.7204301075268817</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7017543859649122</v>
+        <v>0.7282608695652175</v>
       </c>
       <c r="P30" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="S30" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
@@ -3381,46 +3381,46 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="H31" t="n">
         <v>92</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8765432098765432</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7717391304347826</v>
+        <v>0.8152173913043478</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="L31" t="n">
         <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.826530612244898</v>
       </c>
       <c r="N31" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8530805687203792</v>
+        <v>0.8181818181818183</v>
       </c>
       <c r="P31" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S31" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32">
@@ -3442,46 +3442,46 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7239583333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7239583333333334</v>
+        <v>0.75</v>
       </c>
       <c r="H32" t="n">
         <v>89</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6836734693877551</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7528089887640449</v>
+        <v>0.6629213483146067</v>
       </c>
       <c r="K32" t="n">
-        <v>0.716577540106952</v>
+        <v>0.7108433734939759</v>
       </c>
       <c r="L32" t="n">
         <v>103</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6990291262135923</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7309644670050762</v>
+        <v>0.779816513761468</v>
       </c>
       <c r="P32" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="R32" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="S32" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33">
@@ -3503,40 +3503,40 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.828125</v>
+        <v>0.84375</v>
       </c>
       <c r="G33" t="n">
-        <v>0.828125</v>
+        <v>0.84375</v>
       </c>
       <c r="H33" t="n">
         <v>94</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.8404255319148937</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8404255319148937</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8216216216216216</v>
+        <v>0.8404255319148938</v>
       </c>
       <c r="L33" t="n">
         <v>98</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.8469387755102041</v>
       </c>
       <c r="N33" t="n">
         <v>0.8469387755102041</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8341708542713568</v>
+        <v>0.8469387755102041</v>
       </c>
       <c r="P33" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
         <v>15</v>
@@ -3564,34 +3564,34 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.765625</v>
+        <v>0.796875</v>
       </c>
       <c r="G34" t="n">
-        <v>0.765625</v>
+        <v>0.796875</v>
       </c>
       <c r="H34" t="n">
         <v>93</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7448979591836735</v>
+        <v>0.7934782608695652</v>
       </c>
       <c r="J34" t="n">
         <v>0.7849462365591398</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7643979057591623</v>
+        <v>0.7891891891891891</v>
       </c>
       <c r="L34" t="n">
         <v>99</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7474747474747475</v>
+        <v>0.8080808080808081</v>
       </c>
       <c r="O34" t="n">
-        <v>0.766839378238342</v>
+        <v>0.8040201005025126</v>
       </c>
       <c r="P34" t="n">
         <v>73</v>
@@ -3600,10 +3600,10 @@
         <v>20</v>
       </c>
       <c r="R34" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="S34" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -3625,46 +3625,46 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="H35" t="n">
         <v>92</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7339449541284404</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8804347826086957</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7960199004975125</v>
+        <v>0.7864077669902914</v>
       </c>
       <c r="L35" t="n">
         <v>100</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8554216867469879</v>
+        <v>0.8589743589743589</v>
       </c>
       <c r="N35" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7759562841530054</v>
+        <v>0.7528089887640449</v>
       </c>
       <c r="P35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R35" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S35" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
@@ -3695,37 +3695,37 @@
         <v>84</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.75</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7314285714285714</v>
+        <v>0.7283236994219654</v>
       </c>
       <c r="L36" t="n">
         <v>108</v>
       </c>
       <c r="M36" t="n">
-        <v>0.801980198019802</v>
+        <v>0.7961165048543689</v>
       </c>
       <c r="N36" t="n">
-        <v>0.75</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7751196172248804</v>
+        <v>0.7772511848341233</v>
       </c>
       <c r="P36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S36" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
@@ -3747,46 +3747,46 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.71875</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.71875</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7790697674418605</v>
       </c>
       <c r="J37" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7244897959183674</v>
+        <v>0.7204301075268817</v>
       </c>
       <c r="L37" t="n">
         <v>92</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6886792452830188</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7282608695652174</v>
+        <v>0.7934782608695652</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7373737373737372</v>
       </c>
       <c r="P37" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R37" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="S37" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38">
@@ -3808,46 +3808,46 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H38" t="n">
         <v>98</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8061224489795918</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8061224489795918</v>
+        <v>0.7653061224489796</v>
       </c>
       <c r="K38" t="n">
-        <v>0.806122448979592</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="L38" t="n">
         <v>94</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7978723404255319</v>
+        <v>0.780952380952381</v>
       </c>
       <c r="N38" t="n">
-        <v>0.7978723404255319</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7978723404255319</v>
+        <v>0.8241206030150755</v>
       </c>
       <c r="P38" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R38" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S38" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39">
@@ -3869,46 +3869,46 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.78125</v>
+        <v>0.75</v>
       </c>
       <c r="G39" t="n">
-        <v>0.78125</v>
+        <v>0.75</v>
       </c>
       <c r="H39" t="n">
         <v>84</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7019230769230769</v>
+        <v>0.68</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="K39" t="n">
-        <v>0.776595744680851</v>
+        <v>0.7391304347826089</v>
       </c>
       <c r="L39" t="n">
         <v>108</v>
       </c>
       <c r="M39" t="n">
-        <v>0.875</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="N39" t="n">
-        <v>0.7129629629629629</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7857142857142858</v>
+        <v>0.76</v>
       </c>
       <c r="P39" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R39" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S39" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
@@ -3930,46 +3930,46 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H40" t="n">
         <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7410714285714286</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8469387755102041</v>
+        <v>0.826530612244898</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7904761904761906</v>
+        <v>0.7751196172248804</v>
       </c>
       <c r="L40" t="n">
         <v>94</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8125</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6914893617021277</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7471264367816093</v>
+        <v>0.7314285714285713</v>
       </c>
       <c r="P40" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S40" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
@@ -3991,46 +3991,46 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.796875</v>
+        <v>0.78125</v>
       </c>
       <c r="G41" t="n">
-        <v>0.796875</v>
+        <v>0.78125</v>
       </c>
       <c r="H41" t="n">
         <v>105</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8380952380952381</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8186046511627908</v>
+        <v>0.787878787878788</v>
       </c>
       <c r="L41" t="n">
         <v>87</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7926829268292683</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="N41" t="n">
-        <v>0.7471264367816092</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="O41" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="P41" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R41" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="S41" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
@@ -4052,46 +4052,46 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7239583333333334</v>
+        <v>0.734375</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7239583333333334</v>
+        <v>0.734375</v>
       </c>
       <c r="H42" t="n">
         <v>89</v>
       </c>
       <c r="I42" t="n">
-        <v>0.68</v>
+        <v>0.7159090909090909</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7640449438202247</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7195767195767195</v>
+        <v>0.711864406779661</v>
       </c>
       <c r="L42" t="n">
         <v>103</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7717391304347826</v>
+        <v>0.75</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6893203883495146</v>
+        <v>0.7572815533980582</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7282051282051282</v>
+        <v>0.753623188405797</v>
       </c>
       <c r="P42" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R42" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="S42" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43">
@@ -4113,46 +4113,46 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H43" t="n">
         <v>98</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8160919540229885</v>
+        <v>0.8625</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7244897959183674</v>
+        <v>0.7040816326530612</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7675675675675676</v>
+        <v>0.7752808988764046</v>
       </c>
       <c r="L43" t="n">
         <v>94</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7410714285714286</v>
       </c>
       <c r="N43" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8829787234042553</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7839195979899497</v>
+        <v>0.8058252427184466</v>
       </c>
       <c r="P43" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R43" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="S43" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
@@ -4174,46 +4174,46 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H44" t="n">
         <v>111</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8703703703703703</v>
+        <v>0.8380952380952381</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8468468468468469</v>
+        <v>0.7927927927927928</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8584474885844748</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="L44" t="n">
         <v>81</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7976190476190477</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="N44" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="O44" t="n">
-        <v>0.8121212121212122</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="P44" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q44" t="n">
+        <v>23</v>
+      </c>
+      <c r="R44" t="n">
         <v>17</v>
       </c>
-      <c r="R44" t="n">
-        <v>14</v>
-      </c>
       <c r="S44" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
@@ -4235,46 +4235,46 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.84375</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="G45" t="n">
-        <v>0.84375</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="H45" t="n">
         <v>95</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8350515463917526</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="K45" t="n">
-        <v>0.84375</v>
+        <v>0.8379888268156424</v>
       </c>
       <c r="L45" t="n">
         <v>97</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8350515463917526</v>
+        <v>0.9072164948453608</v>
       </c>
       <c r="O45" t="n">
-        <v>0.84375</v>
+        <v>0.8585365853658536</v>
       </c>
       <c r="P45" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R45" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="S45" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
@@ -4296,46 +4296,46 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="H46" t="n">
         <v>102</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7815126050420168</v>
+        <v>0.7565217391304347</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8416289592760181</v>
+        <v>0.8018433179723502</v>
       </c>
       <c r="L46" t="n">
         <v>90</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.8051948051948052</v>
       </c>
       <c r="N46" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7852760736196318</v>
+        <v>0.7425149700598802</v>
       </c>
       <c r="P46" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S46" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
@@ -4357,46 +4357,46 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="H47" t="n">
         <v>99</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="L47" t="n">
         <v>93</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="N47" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="O47" t="n">
-        <v>0.7709497206703911</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="P47" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="Q47" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R47" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S47" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
@@ -4418,46 +4418,46 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7135416666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7135416666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="H48" t="n">
         <v>93</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8279569892473119</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="K48" t="n">
-        <v>0.736842105263158</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="L48" t="n">
         <v>99</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.76</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6857142857142856</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="P48" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R48" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S48" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
@@ -4479,46 +4479,46 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="H49" t="n">
         <v>87</v>
       </c>
       <c r="I49" t="n">
-        <v>0.73</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8390804597701149</v>
+        <v>0.7471264367816092</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7807486631016043</v>
+        <v>0.7027027027027026</v>
       </c>
       <c r="L49" t="n">
         <v>105</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="N49" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7918781725888325</v>
+        <v>0.7236180904522613</v>
       </c>
       <c r="P49" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="R49" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="S49" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
@@ -4549,37 +4549,37 @@
         <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.8255813953488372</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8222222222222223</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="L50" t="n">
         <v>104</v>
       </c>
       <c r="M50" t="n">
-        <v>0.86</v>
+        <v>0.839622641509434</v>
       </c>
       <c r="N50" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.8557692307692307</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8476190476190476</v>
       </c>
       <c r="P50" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R50" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S50" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51">
@@ -4601,40 +4601,40 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9010416666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9010416666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H51" t="n">
         <v>88</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8469387755102041</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9431818181818182</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8983957219251337</v>
+        <v>0.8924731182795699</v>
       </c>
       <c r="L51" t="n">
         <v>104</v>
       </c>
       <c r="M51" t="n">
-        <v>0.956989247311828</v>
+        <v>0.9468085106382979</v>
       </c>
       <c r="N51" t="n">
         <v>0.8557692307692307</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9035532994923857</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="P51" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
         <v>15</v>
@@ -4662,46 +4662,46 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H52" t="n">
         <v>93</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7961165048543689</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8817204301075269</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.836734693877551</v>
       </c>
       <c r="L52" t="n">
         <v>99</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8514851485148515</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="N52" t="n">
-        <v>0.8686868686868687</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="O52" t="n">
-        <v>0.86</v>
+        <v>0.8297872340425531</v>
       </c>
       <c r="P52" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>11</v>
+      </c>
+      <c r="R52" t="n">
+        <v>21</v>
+      </c>
+      <c r="S52" t="n">
         <v>78</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>15</v>
-      </c>
-      <c r="R52" t="n">
-        <v>13</v>
-      </c>
-      <c r="S52" t="n">
-        <v>86</v>
       </c>
     </row>
     <row r="53">
@@ -4723,46 +4723,46 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="H53" t="n">
         <v>95</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7107438016528925</v>
+        <v>0.6991150442477876</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9052631578947369</v>
+        <v>0.8315789473684211</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.7596153846153847</v>
       </c>
       <c r="L53" t="n">
         <v>97</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8732394366197183</v>
+        <v>0.7974683544303798</v>
       </c>
       <c r="N53" t="n">
-        <v>0.6391752577319587</v>
+        <v>0.6494845360824743</v>
       </c>
       <c r="O53" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.7159090909090909</v>
       </c>
       <c r="P53" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R53" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S53" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -4793,37 +4793,37 @@
         <v>99</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7788461538461539</v>
+        <v>0.7685185185185185</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7980295566502463</v>
+        <v>0.8019323671497585</v>
       </c>
       <c r="L54" t="n">
         <v>93</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7954545454545454</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7526881720430108</v>
+        <v>0.7311827956989247</v>
       </c>
       <c r="O54" t="n">
-        <v>0.7734806629834253</v>
+        <v>0.768361581920904</v>
       </c>
       <c r="P54" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R54" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S54" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55">
@@ -4845,46 +4845,46 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.765625</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.765625</v>
       </c>
       <c r="H55" t="n">
         <v>90</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7717391304347826</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7802197802197802</v>
+        <v>0.7540983606557377</v>
       </c>
       <c r="L55" t="n">
         <v>102</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="O55" t="n">
-        <v>0.801980198019802</v>
+        <v>0.7761194029850745</v>
       </c>
       <c r="P55" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S55" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56">
@@ -4906,46 +4906,46 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.828125</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.828125</v>
       </c>
       <c r="H56" t="n">
         <v>94</v>
       </c>
       <c r="I56" t="n">
-        <v>0.794392523364486</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9042553191489362</v>
+        <v>0.8617021276595744</v>
       </c>
       <c r="K56" t="n">
-        <v>0.845771144278607</v>
+        <v>0.8307692307692307</v>
       </c>
       <c r="L56" t="n">
         <v>98</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8941176470588236</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7755102040816326</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="O56" t="n">
-        <v>0.8306010928961749</v>
+        <v>0.8253968253968254</v>
       </c>
       <c r="P56" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="Q56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R56" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S56" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57">
@@ -4967,46 +4967,46 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.828125</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="G57" t="n">
-        <v>0.828125</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="H57" t="n">
         <v>95</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8315789473684211</v>
+        <v>0.8736842105263158</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8272251308900523</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="L57" t="n">
         <v>97</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8736842105263158</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8290155440414508</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="P57" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R57" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="S57" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58">
@@ -5028,46 +5028,46 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H58" t="n">
         <v>91</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7889908256880734</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="J58" t="n">
-        <v>0.945054945054945</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.8279569892473119</v>
       </c>
       <c r="L58" t="n">
         <v>101</v>
       </c>
       <c r="M58" t="n">
-        <v>0.9397590361445783</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="N58" t="n">
-        <v>0.7722772277227723</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8478260869565218</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="P58" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R58" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="S58" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59">
@@ -5089,46 +5089,46 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="H59" t="n">
         <v>88</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9431818181818182</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8383838383838385</v>
+        <v>0.8554913294797689</v>
       </c>
       <c r="L59" t="n">
         <v>104</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9390243902439024</v>
+        <v>0.8691588785046729</v>
       </c>
       <c r="N59" t="n">
-        <v>0.7403846153846154</v>
+        <v>0.8942307692307693</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8279569892473119</v>
+        <v>0.881516587677725</v>
       </c>
       <c r="P59" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R59" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="S59" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
@@ -5150,46 +5150,46 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="H60" t="n">
         <v>111</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8454545454545455</v>
+        <v>0.9058823529411765</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8378378378378378</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="K60" t="n">
-        <v>0.841628959276018</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="L60" t="n">
         <v>81</v>
       </c>
       <c r="M60" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.6822429906542056</v>
       </c>
       <c r="N60" t="n">
-        <v>0.7901234567901234</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7852760736196319</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="P60" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="Q60" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="R60" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S60" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61">
@@ -5211,46 +5211,46 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H61" t="n">
         <v>98</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8673469387755102</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7981220657276995</v>
+        <v>0.7539267015706805</v>
       </c>
       <c r="L61" t="n">
         <v>94</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8311688311688312</v>
+        <v>0.7373737373737373</v>
       </c>
       <c r="N61" t="n">
-        <v>0.6808510638297872</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7485380116959065</v>
+        <v>0.7564766839378237</v>
       </c>
       <c r="P61" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="Q61" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="R61" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="S61" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
@@ -5272,46 +5272,46 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H62" t="n">
         <v>106</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7889908256880734</v>
+        <v>0.8317757009345794</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.839622641509434</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8356807511737089</v>
       </c>
       <c r="L62" t="n">
         <v>86</v>
       </c>
       <c r="M62" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.8</v>
       </c>
       <c r="N62" t="n">
-        <v>0.7325581395348837</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="O62" t="n">
-        <v>0.7455621301775147</v>
+        <v>0.7953216374269007</v>
       </c>
       <c r="P62" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R62" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="S62" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
@@ -5333,46 +5333,46 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="H63" t="n">
         <v>88</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7052631578947368</v>
       </c>
       <c r="J63" t="n">
-        <v>0.75</v>
+        <v>0.7613636363636364</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7415730337078651</v>
+        <v>0.7322404371584699</v>
       </c>
       <c r="L63" t="n">
         <v>104</v>
       </c>
       <c r="M63" t="n">
-        <v>0.7843137254901961</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="N63" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="O63" t="n">
-        <v>0.7766990291262137</v>
+        <v>0.7562189054726368</v>
       </c>
       <c r="P63" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R63" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="S63" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64">
@@ -5394,46 +5394,46 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H64" t="n">
         <v>91</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.7160493827160493</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.6373626373626373</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7231638418079095</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="L64" t="n">
         <v>101</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7452830188679245</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="N64" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7722772277227723</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7632850241545893</v>
+        <v>0.7358490566037735</v>
       </c>
       <c r="P64" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q64" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="R64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S64" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
@@ -5455,46 +5455,46 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.78125</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="G65" t="n">
-        <v>0.78125</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H65" t="n">
         <v>95</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7623762376237624</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8105263157894737</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="K65" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.783068783068783</v>
       </c>
       <c r="L65" t="n">
         <v>97</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8021978021978022</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N65" t="n">
-        <v>0.7525773195876289</v>
+        <v>0.7938144329896907</v>
       </c>
       <c r="O65" t="n">
-        <v>0.7765957446808511</v>
+        <v>0.7897435897435898</v>
       </c>
       <c r="P65" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>21</v>
+      </c>
+      <c r="R65" t="n">
+        <v>20</v>
+      </c>
+      <c r="S65" t="n">
         <v>77</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>18</v>
-      </c>
-      <c r="R65" t="n">
-        <v>24</v>
-      </c>
-      <c r="S65" t="n">
-        <v>73</v>
       </c>
     </row>
     <row r="66">
@@ -5516,46 +5516,46 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.84375</v>
+        <v>0.8125</v>
       </c>
       <c r="G66" t="n">
-        <v>0.84375</v>
+        <v>0.8125</v>
       </c>
       <c r="H66" t="n">
         <v>83</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7849462365591398</v>
+        <v>0.7640449438202247</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8795180722891566</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="K66" t="n">
-        <v>0.8295454545454544</v>
+        <v>0.7906976744186045</v>
       </c>
       <c r="L66" t="n">
         <v>109</v>
       </c>
       <c r="M66" t="n">
-        <v>0.898989898989899</v>
+        <v>0.8543689320388349</v>
       </c>
       <c r="N66" t="n">
-        <v>0.8165137614678899</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8557692307692307</v>
+        <v>0.8301886792452829</v>
       </c>
       <c r="P66" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S66" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67">
@@ -5577,46 +5577,46 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H67" t="n">
         <v>92</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J67" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.7539267015706806</v>
       </c>
       <c r="L67" t="n">
         <v>100</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8173076923076923</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="N67" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="O67" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7564766839378239</v>
       </c>
       <c r="P67" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>20</v>
+      </c>
+      <c r="R67" t="n">
+        <v>27</v>
+      </c>
+      <c r="S67" t="n">
         <v>73</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>19</v>
-      </c>
-      <c r="R67" t="n">
-        <v>15</v>
-      </c>
-      <c r="S67" t="n">
-        <v>85</v>
       </c>
     </row>
     <row r="68">
@@ -5638,46 +5638,46 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="H68" t="n">
         <v>98</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8877551020408163</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="K68" t="n">
-        <v>0.8093023255813954</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="L68" t="n">
         <v>94</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6808510638297872</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="O68" t="n">
-        <v>0.757396449704142</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="P68" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="Q68" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R68" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="S68" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
@@ -5699,46 +5699,46 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H69" t="n">
         <v>94</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8354430379746836</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="K69" t="n">
-        <v>0.839378238341969</v>
+        <v>0.7630057803468209</v>
       </c>
       <c r="L69" t="n">
         <v>98</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8602150537634409</v>
+        <v>0.7522123893805309</v>
       </c>
       <c r="N69" t="n">
-        <v>0.8163265306122449</v>
+        <v>0.8673469387755102</v>
       </c>
       <c r="O69" t="n">
-        <v>0.837696335078534</v>
+        <v>0.8056872037914692</v>
       </c>
       <c r="P69" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="Q69" t="n">
+        <v>28</v>
+      </c>
+      <c r="R69" t="n">
         <v>13</v>
       </c>
-      <c r="R69" t="n">
-        <v>18</v>
-      </c>
       <c r="S69" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70">
@@ -5760,34 +5760,34 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.84375</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="G70" t="n">
-        <v>0.84375</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="H70" t="n">
         <v>83</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7912087912087912</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="J70" t="n">
         <v>0.8674698795180723</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8275862068965518</v>
+        <v>0.822857142857143</v>
       </c>
       <c r="L70" t="n">
         <v>109</v>
       </c>
       <c r="M70" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.89</v>
       </c>
       <c r="N70" t="n">
-        <v>0.8256880733944955</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8516746411483254</v>
       </c>
       <c r="P70" t="n">
         <v>72</v>
@@ -5796,10 +5796,10 @@
         <v>11</v>
       </c>
       <c r="R70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S70" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71">
@@ -5830,37 +5830,37 @@
         <v>93</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8202247191011236</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="J71" t="n">
-        <v>0.7849462365591398</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8021978021978021</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="L71" t="n">
         <v>99</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8058252427184466</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="N71" t="n">
-        <v>0.8383838383838383</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="O71" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.8378378378378378</v>
       </c>
       <c r="P71" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="Q71" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R71" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S71" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="72">
@@ -5882,46 +5882,46 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="G72" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="H72" t="n">
         <v>101</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7452830188679245</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="J72" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.6831683168316832</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7632850241545893</v>
+        <v>0.75</v>
       </c>
       <c r="L72" t="n">
         <v>91</v>
       </c>
       <c r="M72" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.7064220183486238</v>
       </c>
       <c r="N72" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="O72" t="n">
-        <v>0.7231638418079095</v>
+        <v>0.7699999999999999</v>
       </c>
       <c r="P72" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="Q72" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="R72" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="S72" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73">
@@ -5943,46 +5943,46 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.84375</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="G73" t="n">
-        <v>0.84375</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H73" t="n">
         <v>105</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8504672897196262</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8380952380952381</v>
       </c>
       <c r="K73" t="n">
-        <v>0.8584905660377359</v>
+        <v>0.8224299065420561</v>
       </c>
       <c r="L73" t="n">
         <v>87</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8352941176470589</v>
+        <v>0.7951807228915663</v>
       </c>
       <c r="N73" t="n">
-        <v>0.8160919540229885</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="O73" t="n">
-        <v>0.8255813953488372</v>
+        <v>0.7764705882352942</v>
       </c>
       <c r="P73" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q73" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R73" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="S73" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74">
@@ -6004,46 +6004,46 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.71875</v>
+        <v>0.734375</v>
       </c>
       <c r="G74" t="n">
-        <v>0.71875</v>
+        <v>0.734375</v>
       </c>
       <c r="H74" t="n">
         <v>84</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6701030927835051</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7187499999999999</v>
+        <v>0.718232044198895</v>
       </c>
       <c r="L74" t="n">
         <v>108</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8</v>
       </c>
       <c r="N74" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7187499999999999</v>
+        <v>0.7487684729064039</v>
       </c>
       <c r="P74" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R74" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="S74" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75">
@@ -6065,40 +6065,40 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="H75" t="n">
         <v>99</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.78</v>
       </c>
       <c r="J75" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7839195979899497</v>
       </c>
       <c r="L75" t="n">
         <v>93</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7473684210526316</v>
+        <v>0.7717391304347826</v>
       </c>
       <c r="N75" t="n">
         <v>0.7634408602150538</v>
       </c>
       <c r="O75" t="n">
-        <v>0.7553191489361704</v>
+        <v>0.7675675675675675</v>
       </c>
       <c r="P75" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R75" t="n">
         <v>22</v>
@@ -6126,46 +6126,46 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="H76" t="n">
         <v>99</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8252427184466019</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="K76" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.8497409326424871</v>
       </c>
       <c r="L76" t="n">
         <v>93</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8426966292134831</v>
+        <v>0.826530612244898</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="O76" t="n">
-        <v>0.8241758241758241</v>
+        <v>0.8481675392670157</v>
       </c>
       <c r="P76" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q76" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R76" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S76" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77">
@@ -6196,37 +6196,37 @@
         <v>97</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.7676767676767676</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8041237113402062</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="K77" t="n">
-        <v>0.78</v>
+        <v>0.7755102040816326</v>
       </c>
       <c r="L77" t="n">
         <v>95</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7865168539325843</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="N77" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7578947368421053</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.7659574468085107</v>
       </c>
       <c r="P77" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q77" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R77" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S77" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78">
@@ -6248,46 +6248,46 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="H78" t="n">
         <v>111</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8362068965517241</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8468468468468469</v>
+        <v>0.8738738738738738</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8430493273542602</v>
+        <v>0.8546255506607928</v>
       </c>
       <c r="L78" t="n">
         <v>81</v>
       </c>
       <c r="M78" t="n">
-        <v>0.7875</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="N78" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="O78" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7898089171974522</v>
       </c>
       <c r="P78" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q78" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S78" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79">
@@ -6309,40 +6309,40 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.796875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G79" t="n">
-        <v>0.796875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H79" t="n">
         <v>94</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7755102040816326</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="K79" t="n">
-        <v>0.7979274611398963</v>
+        <v>0.7916666666666665</v>
       </c>
       <c r="L79" t="n">
         <v>98</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8172043010752689</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="N79" t="n">
         <v>0.7755102040816326</v>
       </c>
       <c r="O79" t="n">
-        <v>0.7958115183246073</v>
+        <v>0.7916666666666665</v>
       </c>
       <c r="P79" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R79" t="n">
         <v>22</v>
@@ -6370,46 +6370,46 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H80" t="n">
         <v>87</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6831683168316832</v>
+        <v>0.788235294117647</v>
       </c>
       <c r="J80" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.7701149425287356</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.7790697674418604</v>
       </c>
       <c r="L80" t="n">
         <v>105</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8021978021978022</v>
+        <v>0.8130841121495327</v>
       </c>
       <c r="N80" t="n">
-        <v>0.6952380952380952</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7448979591836735</v>
+        <v>0.820754716981132</v>
       </c>
       <c r="P80" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q80" t="n">
+        <v>20</v>
+      </c>
+      <c r="R80" t="n">
         <v>18</v>
       </c>
-      <c r="R80" t="n">
-        <v>32</v>
-      </c>
       <c r="S80" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81">
@@ -6431,40 +6431,40 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="H81" t="n">
         <v>92</v>
       </c>
       <c r="I81" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8152173913043478</v>
+        <v>0.7934782608695652</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7853403141361256</v>
+        <v>0.7724867724867726</v>
       </c>
       <c r="L81" t="n">
         <v>100</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8172043010752689</v>
+        <v>0.8</v>
       </c>
       <c r="N81" t="n">
         <v>0.76</v>
       </c>
       <c r="O81" t="n">
-        <v>0.7875647668393783</v>
+        <v>0.7794871794871796</v>
       </c>
       <c r="P81" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q81" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R81" t="n">
         <v>24</v>
@@ -6492,46 +6492,46 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H82" t="n">
         <v>84</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6627906976744187</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="L82" t="n">
         <v>108</v>
       </c>
       <c r="M82" t="n">
-        <v>0.7403846153846154</v>
+        <v>0.72</v>
       </c>
       <c r="N82" t="n">
-        <v>0.7129629629629629</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O82" t="n">
-        <v>0.7264150943396226</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P82" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R82" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S82" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83">
@@ -6553,46 +6553,46 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H83" t="n">
         <v>94</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7755102040816326</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="K83" t="n">
-        <v>0.7916666666666665</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="L83" t="n">
         <v>98</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8061224489795918</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7755102040816326</v>
+        <v>0.8061224489795918</v>
       </c>
       <c r="O83" t="n">
-        <v>0.7916666666666665</v>
+        <v>0.806122448979592</v>
       </c>
       <c r="P83" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R83" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="S83" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84">
@@ -6614,34 +6614,34 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="H84" t="n">
         <v>103</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="J84" t="n">
         <v>0.8446601941747572</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8613861386138614</v>
+        <v>0.848780487804878</v>
       </c>
       <c r="L84" t="n">
         <v>89</v>
       </c>
       <c r="M84" t="n">
-        <v>0.8279569892473119</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="N84" t="n">
-        <v>0.8651685393258427</v>
+        <v>0.8314606741573034</v>
       </c>
       <c r="O84" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8268156424581005</v>
       </c>
       <c r="P84" t="n">
         <v>87</v>
@@ -6650,10 +6650,10 @@
         <v>16</v>
       </c>
       <c r="R84" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S84" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85">
@@ -6675,46 +6675,46 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="G85" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="H85" t="n">
         <v>107</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7927927927927928</v>
       </c>
       <c r="J85" t="n">
-        <v>0.7850467289719626</v>
+        <v>0.8224299065420561</v>
       </c>
       <c r="K85" t="n">
-        <v>0.8038277511961723</v>
+        <v>0.8073394495412843</v>
       </c>
       <c r="L85" t="n">
         <v>85</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="N85" t="n">
-        <v>0.788235294117647</v>
+        <v>0.7294117647058823</v>
       </c>
       <c r="O85" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7469879518072289</v>
       </c>
       <c r="P85" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q85" t="n">
+        <v>19</v>
+      </c>
+      <c r="R85" t="n">
         <v>23</v>
       </c>
-      <c r="R85" t="n">
-        <v>18</v>
-      </c>
       <c r="S85" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86">
@@ -6745,37 +6745,37 @@
         <v>101</v>
       </c>
       <c r="I86" t="n">
-        <v>0.7961165048543689</v>
+        <v>0.7798165137614679</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8118811881188119</v>
+        <v>0.8415841584158416</v>
       </c>
       <c r="K86" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L86" t="n">
         <v>91</v>
       </c>
       <c r="M86" t="n">
-        <v>0.7865168539325843</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="N86" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7362637362637363</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7701149425287357</v>
       </c>
       <c r="P86" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q86" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S86" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
@@ -6806,37 +6806,37 @@
         <v>97</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8224299065420561</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9072164948453608</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.86</v>
       </c>
       <c r="L87" t="n">
         <v>95</v>
       </c>
       <c r="M87" t="n">
-        <v>0.8941176470588236</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="N87" t="n">
-        <v>0.8</v>
+        <v>0.8210526315789474</v>
       </c>
       <c r="O87" t="n">
-        <v>0.8444444444444443</v>
+        <v>0.8478260869565217</v>
       </c>
       <c r="P87" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q87" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R87" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S87" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88">
@@ -6858,46 +6858,46 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.7904761904761904</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8316831683168316</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="K88" t="n">
-        <v>0.7924528301886792</v>
+        <v>0.8058252427184466</v>
       </c>
       <c r="L88" t="n">
         <v>91</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7901234567901234</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="N88" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.7582417582417582</v>
       </c>
       <c r="O88" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.7752808988764045</v>
       </c>
       <c r="P88" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R88" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="S88" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="89">
@@ -6928,37 +6928,37 @@
         <v>103</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7676767676767676</v>
+        <v>0.7623762376237624</v>
       </c>
       <c r="J89" t="n">
-        <v>0.7378640776699029</v>
+        <v>0.7475728155339806</v>
       </c>
       <c r="K89" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.7549019607843138</v>
       </c>
       <c r="L89" t="n">
         <v>89</v>
       </c>
       <c r="M89" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7415730337078652</v>
+        <v>0.7303370786516854</v>
       </c>
       <c r="O89" t="n">
-        <v>0.7252747252747254</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="P89" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S89" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90">
@@ -6980,46 +6980,46 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H90" t="n">
         <v>100</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="J90" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="K90" t="n">
-        <v>0.8241206030150754</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="L90" t="n">
         <v>92</v>
       </c>
       <c r="M90" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.75</v>
       </c>
       <c r="N90" t="n">
-        <v>0.8152173913043478</v>
+        <v>0.8478260869565217</v>
       </c>
       <c r="O90" t="n">
-        <v>0.8108108108108107</v>
+        <v>0.7959183673469389</v>
       </c>
       <c r="P90" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q90" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="R90" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="S90" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91">
@@ -7041,46 +7041,46 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="G91" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="H91" t="n">
         <v>105</v>
       </c>
       <c r="I91" t="n">
-        <v>0.797979797979798</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="J91" t="n">
-        <v>0.7523809523809524</v>
+        <v>0.819047619047619</v>
       </c>
       <c r="K91" t="n">
-        <v>0.7745098039215685</v>
+        <v>0.8037383177570094</v>
       </c>
       <c r="L91" t="n">
         <v>87</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7204301075268817</v>
+        <v>0.7710843373493976</v>
       </c>
       <c r="N91" t="n">
-        <v>0.7701149425287356</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="O91" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7529411764705882</v>
       </c>
       <c r="P91" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="Q91" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="R91" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S91" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92">
@@ -7102,46 +7102,46 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="G92" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="H92" t="n">
         <v>106</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="J92" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.8301886792452831</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8380952380952382</v>
       </c>
       <c r="L92" t="n">
         <v>86</v>
       </c>
       <c r="M92" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="N92" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8</v>
+        <v>0.8045977011494252</v>
       </c>
       <c r="P92" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="Q92" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R92" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="S92" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
@@ -7163,46 +7163,46 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="G93" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="H93" t="n">
         <v>103</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8557692307692307</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
-        <v>0.8640776699029126</v>
+        <v>0.7864077669902912</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8599033816425121</v>
+        <v>0.8393782383419689</v>
       </c>
       <c r="L93" t="n">
         <v>89</v>
       </c>
       <c r="M93" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="N93" t="n">
-        <v>0.8314606741573034</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="O93" t="n">
-        <v>0.8361581920903954</v>
+        <v>0.837696335078534</v>
       </c>
       <c r="P93" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Q93" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="R93" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="S93" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94">
@@ -7224,46 +7224,46 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.796875</v>
+        <v>0.8125</v>
       </c>
       <c r="G94" t="n">
-        <v>0.796875</v>
+        <v>0.8125</v>
       </c>
       <c r="H94" t="n">
         <v>104</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8207547169811321</v>
       </c>
       <c r="J94" t="n">
-        <v>0.875</v>
+        <v>0.8365384615384616</v>
       </c>
       <c r="K94" t="n">
-        <v>0.823529411764706</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="L94" t="n">
         <v>88</v>
       </c>
       <c r="M94" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="N94" t="n">
-        <v>0.7045454545454546</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="O94" t="n">
-        <v>0.7607361963190183</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="P94" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="Q94" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R94" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="S94" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95">
@@ -7285,46 +7285,46 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.796875</v>
+        <v>0.828125</v>
       </c>
       <c r="G95" t="n">
-        <v>0.796875</v>
+        <v>0.828125</v>
       </c>
       <c r="H95" t="n">
         <v>96</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7766990291262136</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="J95" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="K95" t="n">
-        <v>0.8040201005025125</v>
+        <v>0.8196721311475409</v>
       </c>
       <c r="L95" t="n">
         <v>96</v>
       </c>
       <c r="M95" t="n">
-        <v>0.8202247191011236</v>
+        <v>0.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.875</v>
       </c>
       <c r="O95" t="n">
-        <v>0.7891891891891892</v>
+        <v>0.8358208955223881</v>
       </c>
       <c r="P95" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q95" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R95" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S95" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96">
@@ -7346,46 +7346,46 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="G96" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H96" t="n">
         <v>94</v>
       </c>
       <c r="I96" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8586956521739131</v>
       </c>
       <c r="J96" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8404255319148937</v>
       </c>
       <c r="K96" t="n">
-        <v>0.8602150537634409</v>
+        <v>0.849462365591398</v>
       </c>
       <c r="L96" t="n">
         <v>98</v>
       </c>
       <c r="M96" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="N96" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8673469387755102</v>
       </c>
       <c r="O96" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.8585858585858585</v>
       </c>
       <c r="P96" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S96" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97">
@@ -7407,46 +7407,46 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="H97" t="n">
         <v>94</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="J97" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="K97" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="L97" t="n">
         <v>98</v>
       </c>
       <c r="M97" t="n">
-        <v>0.826530612244898</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="N97" t="n">
-        <v>0.826530612244898</v>
+        <v>0.7755102040816326</v>
       </c>
       <c r="O97" t="n">
-        <v>0.826530612244898</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="P97" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q97" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R97" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S97" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="98">
@@ -7468,46 +7468,46 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H98" t="n">
         <v>90</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7653061224489796</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K98" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="L98" t="n">
         <v>102</v>
       </c>
       <c r="M98" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.8404255319148937</v>
       </c>
       <c r="N98" t="n">
-        <v>0.7549019607843137</v>
+        <v>0.7745098039215687</v>
       </c>
       <c r="O98" t="n">
-        <v>0.8148148148148149</v>
+        <v>0.806122448979592</v>
       </c>
       <c r="P98" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R98" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S98" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99">
@@ -7529,46 +7529,46 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="H99" t="n">
         <v>101</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8977272727272727</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="J99" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="K99" t="n">
-        <v>0.835978835978836</v>
+        <v>0.8021390374331551</v>
       </c>
       <c r="L99" t="n">
         <v>91</v>
       </c>
       <c r="M99" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.7547169811320755</v>
       </c>
       <c r="N99" t="n">
-        <v>0.9010989010989011</v>
+        <v>0.8791208791208791</v>
       </c>
       <c r="O99" t="n">
-        <v>0.841025641025641</v>
+        <v>0.8121827411167513</v>
       </c>
       <c r="P99" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q99" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S99" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100">
@@ -7590,46 +7590,46 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="G100" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="H100" t="n">
         <v>90</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8433734939759037</v>
       </c>
       <c r="J100" t="n">
-        <v>0.8</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K100" t="n">
-        <v>0.8323699421965319</v>
+        <v>0.8092485549132947</v>
       </c>
       <c r="L100" t="n">
         <v>102</v>
       </c>
       <c r="M100" t="n">
-        <v>0.8348623853211009</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="N100" t="n">
-        <v>0.8921568627450981</v>
+        <v>0.8725490196078431</v>
       </c>
       <c r="O100" t="n">
-        <v>0.8625592417061612</v>
+        <v>0.8436018957345972</v>
       </c>
       <c r="P100" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q100" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R100" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S100" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="101">
@@ -7651,34 +7651,34 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7552083333333334</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7552083333333334</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H101" t="n">
         <v>98</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7475728155339806</v>
+        <v>0.7129629629629629</v>
       </c>
       <c r="J101" t="n">
         <v>0.7857142857142857</v>
       </c>
       <c r="K101" t="n">
-        <v>0.7661691542288557</v>
+        <v>0.7475728155339806</v>
       </c>
       <c r="L101" t="n">
         <v>94</v>
       </c>
       <c r="M101" t="n">
-        <v>0.7640449438202247</v>
+        <v>0.75</v>
       </c>
       <c r="N101" t="n">
-        <v>0.723404255319149</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="O101" t="n">
-        <v>0.7431693989071038</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="P101" t="n">
         <v>77</v>
@@ -7687,10 +7687,10 @@
         <v>21</v>
       </c>
       <c r="R101" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="S101" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -7726,10 +7726,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7875</v>
+        <v>7536</v>
       </c>
       <c r="C2" t="n">
-        <v>1679</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="3">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2247</v>
+        <v>2057</v>
       </c>
       <c r="C3" t="n">
-        <v>7399</v>
+        <v>7589</v>
       </c>
     </row>
   </sheetData>
@@ -7793,16 +7793,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
@@ -7812,16 +7812,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">
@@ -7831,16 +7831,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C4" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" t="n">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E4" t="n">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="D5" t="n">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="E5" t="n">
-        <v>493</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6">
@@ -7869,16 +7869,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="E6" t="n">
-        <v>553</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7">
@@ -7888,16 +7888,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>717</v>
+        <v>679</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>797</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -7907,16 +7907,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>770</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9">
@@ -7926,16 +7926,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E9" t="n">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10">
@@ -7945,16 +7945,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="E10" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11">
@@ -7964,16 +7964,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="C11" t="n">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="D11" t="n">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E11" t="n">
-        <v>571</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12">
@@ -7983,16 +7983,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
-        <v>745</v>
+        <v>755</v>
       </c>
     </row>
     <row r="13">
@@ -8002,16 +8002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>630</v>
+        <v>593</v>
       </c>
       <c r="C13" t="n">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="D13" t="n">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="E13" t="n">
-        <v>517</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14">
@@ -8021,16 +8021,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>590</v>
+        <v>496</v>
       </c>
       <c r="C14" t="n">
-        <v>178</v>
+        <v>272</v>
       </c>
       <c r="D14" t="n">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="E14" t="n">
-        <v>618</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
